--- a/P&L_Rent_Projects_F.xlsx
+++ b/P&L_Rent_Projects_F.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\سدرة الخير\Hub Project Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7960E914-EA60-42F2-A0F4-CCCA1A12AAD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E334EEC1-2E13-4689-A15C-868AD277EFB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{D8720DA4-03DD-471F-8DC0-E7471CF99247}"/>
   </bookViews>
@@ -121,7 +121,7 @@
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* \-??_);_(@_)"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -174,13 +174,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -506,7 +499,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -536,39 +529,38 @@
     <xf numFmtId="165" fontId="3" fillId="4" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="3" fillId="4" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="2" fillId="3" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="5" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="6" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="3" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="11" fillId="3" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -890,720 +882,711 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3488CD7C-8A5C-4EE4-8C4C-F7117492D1F2}">
-  <dimension ref="A3:N24"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="6" customWidth="1"/>
-    <col min="3" max="3" width="36.44140625" customWidth="1"/>
-    <col min="4" max="13" width="12.77734375" customWidth="1"/>
-    <col min="14" max="14" width="15.33203125" customWidth="1"/>
+    <col min="1" max="1" width="36.44140625" customWidth="1"/>
+    <col min="2" max="11" width="12.77734375" customWidth="1"/>
+    <col min="12" max="12" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="D3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="3" t="s">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="D4" s="5"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="7"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C5" s="8" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B2" s="5"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="7"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="9">
+      <c r="B3" s="9">
         <v>13</v>
       </c>
-      <c r="E5" s="10">
+      <c r="C3" s="10">
         <v>28</v>
       </c>
-      <c r="F5" s="10">
+      <c r="D3" s="10">
         <v>41</v>
       </c>
-      <c r="G5" s="10">
+      <c r="E3" s="10">
         <v>18</v>
       </c>
-      <c r="H5" s="10">
+      <c r="F3" s="10">
         <v>31</v>
       </c>
-      <c r="I5" s="10">
+      <c r="G3" s="10">
         <v>48</v>
       </c>
-      <c r="J5" s="10">
+      <c r="H3" s="10">
         <v>9</v>
       </c>
-      <c r="K5" s="10">
+      <c r="I3" s="10">
         <v>51</v>
       </c>
-      <c r="L5" s="10">
+      <c r="J3" s="10">
         <v>10</v>
       </c>
-      <c r="M5" s="10">
+      <c r="K3" s="10">
         <v>14</v>
       </c>
-      <c r="N5" s="11">
+      <c r="L3" s="11">
         <v>263</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C6" s="8" t="s">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="12">
+      <c r="B4" s="12">
         <v>8</v>
       </c>
-      <c r="E6" s="13">
+      <c r="C4" s="13">
         <v>22</v>
       </c>
-      <c r="F6" s="13">
+      <c r="D4" s="13">
         <v>34</v>
       </c>
-      <c r="G6" s="13">
+      <c r="E4" s="13">
         <v>18</v>
       </c>
-      <c r="H6" s="13">
+      <c r="F4" s="13">
         <v>30</v>
       </c>
-      <c r="I6" s="13">
+      <c r="G4" s="13">
         <v>48</v>
       </c>
-      <c r="J6" s="13">
+      <c r="H4" s="13">
         <v>7</v>
       </c>
-      <c r="K6" s="13">
+      <c r="I4" s="13">
         <v>51</v>
       </c>
-      <c r="L6" s="13">
+      <c r="J4" s="13">
         <v>9</v>
       </c>
-      <c r="M6" s="13">
+      <c r="K4" s="13">
         <v>14</v>
       </c>
-      <c r="N6" s="14">
+      <c r="L4" s="14">
         <v>241</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C7" s="8" t="s">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="15">
+      <c r="B5" s="15">
         <v>0.61538461538461542</v>
       </c>
-      <c r="E7" s="16">
+      <c r="C5" s="16">
         <v>0.7857142857142857</v>
       </c>
-      <c r="F7" s="16">
+      <c r="D5" s="16">
         <v>0.82926829268292679</v>
       </c>
-      <c r="G7" s="16">
+      <c r="E5" s="16">
         <v>1</v>
       </c>
-      <c r="H7" s="16">
+      <c r="F5" s="16">
         <v>0.967741935483871</v>
       </c>
-      <c r="I7" s="16">
+      <c r="G5" s="16">
         <v>1</v>
       </c>
-      <c r="J7" s="16">
+      <c r="H5" s="16">
         <v>0.77777777777777779</v>
       </c>
-      <c r="K7" s="16">
+      <c r="I5" s="16">
         <v>1</v>
       </c>
-      <c r="L7" s="16">
+      <c r="J5" s="16">
         <v>0.9</v>
       </c>
-      <c r="M7" s="16">
+      <c r="K5" s="16">
         <v>1</v>
       </c>
-      <c r="N7" s="17">
+      <c r="L5" s="17">
         <v>0.91634980988593151</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C8" s="8" t="s">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="18">
+      <c r="B6" s="18">
         <v>263984.25</v>
       </c>
-      <c r="E8" s="19">
+      <c r="C6" s="19">
         <v>1053228.27</v>
       </c>
-      <c r="F8" s="19">
+      <c r="D6" s="19">
         <v>563328.69999999995</v>
       </c>
-      <c r="G8" s="19">
+      <c r="E6" s="19">
         <v>876392.56</v>
       </c>
-      <c r="H8" s="19">
+      <c r="F6" s="19">
         <v>300146.36</v>
       </c>
-      <c r="I8" s="19">
+      <c r="G6" s="19">
         <v>250000</v>
       </c>
-      <c r="J8" s="19">
+      <c r="H6" s="19">
         <v>220379.96</v>
       </c>
-      <c r="K8" s="19">
+      <c r="I6" s="19">
         <v>716213.33000000007</v>
       </c>
-      <c r="L8" s="19">
+      <c r="J6" s="19">
         <v>335924.65</v>
       </c>
-      <c r="M8" s="19">
+      <c r="K6" s="19">
         <v>654450.31999999995</v>
       </c>
-      <c r="N8" s="20">
+      <c r="L6" s="20">
         <v>5234048.4000000004</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="21"/>
-      <c r="C10" s="22" t="s">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="23">
+      <c r="B8" s="22">
         <v>242833</v>
       </c>
-      <c r="E10" s="23">
+      <c r="C8" s="22">
         <v>209506</v>
       </c>
-      <c r="F10" s="23">
+      <c r="D8" s="22">
         <v>1063845</v>
       </c>
-      <c r="G10" s="23">
+      <c r="E8" s="22">
         <v>192118</v>
       </c>
-      <c r="H10" s="23">
+      <c r="F8" s="22">
         <v>320457</v>
       </c>
-      <c r="I10" s="23">
+      <c r="G8" s="22">
         <v>371434</v>
       </c>
-      <c r="J10" s="23">
+      <c r="H8" s="22">
         <v>167663</v>
       </c>
-      <c r="K10" s="23">
+      <c r="I8" s="22">
         <v>2077101</v>
       </c>
-      <c r="L10" s="23">
+      <c r="J8" s="22">
         <v>98000</v>
       </c>
-      <c r="M10" s="23">
+      <c r="K8" s="22">
         <v>140867</v>
       </c>
-      <c r="N10" s="24">
+      <c r="L8" s="23">
         <v>4883824</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C11" s="25"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
-      <c r="I11" s="26"/>
-      <c r="J11" s="26"/>
-      <c r="K11" s="26"/>
-      <c r="L11" s="26"/>
-      <c r="M11" s="26"/>
-      <c r="N11" s="27"/>
-    </row>
-    <row r="12" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C12" s="37" t="s">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="24"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="26"/>
+    </row>
+    <row r="10" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="38"/>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="L12" s="38"/>
-      <c r="M12" s="38"/>
-      <c r="N12" s="39"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C13" s="28" t="s">
+      <c r="B10" s="37"/>
+      <c r="C10" s="37"/>
+      <c r="D10" s="37"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="37"/>
+      <c r="H10" s="37"/>
+      <c r="I10" s="37"/>
+      <c r="J10" s="37"/>
+      <c r="K10" s="37"/>
+      <c r="L10" s="38"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="29">
+      <c r="B11" s="28">
         <v>390962.95</v>
       </c>
-      <c r="E13" s="29">
+      <c r="C11" s="28">
         <v>585395.39</v>
       </c>
-      <c r="F13" s="29">
+      <c r="D11" s="28">
         <v>811993.8899999999</v>
       </c>
-      <c r="G13" s="29">
+      <c r="E11" s="28">
         <v>223638.29</v>
       </c>
-      <c r="H13" s="29">
+      <c r="F11" s="28">
         <v>228948.65</v>
       </c>
-      <c r="I13" s="29">
+      <c r="G11" s="28">
         <v>560173.66</v>
       </c>
-      <c r="J13" s="29">
+      <c r="H11" s="28">
         <v>144055.4</v>
       </c>
-      <c r="K13" s="29">
+      <c r="I11" s="28">
         <v>1344225.42</v>
       </c>
-      <c r="L13" s="29">
+      <c r="J11" s="28">
         <v>185000</v>
       </c>
-      <c r="M13" s="29">
+      <c r="K11" s="28">
         <v>100030</v>
       </c>
-      <c r="N13" s="30">
+      <c r="L11" s="29">
         <v>4574423.6500000004</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="21"/>
-      <c r="C14" s="31" t="s">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="32">
+      <c r="B12" s="31">
         <v>350000</v>
       </c>
-      <c r="E14" s="32">
+      <c r="C12" s="31">
         <v>550000</v>
       </c>
-      <c r="F14" s="32">
+      <c r="D12" s="31">
         <v>750000</v>
       </c>
-      <c r="G14" s="32">
+      <c r="E12" s="31">
         <v>200000</v>
       </c>
-      <c r="H14" s="32">
+      <c r="F12" s="31">
         <v>200000</v>
       </c>
-      <c r="I14" s="32">
+      <c r="G12" s="31">
         <v>510000</v>
       </c>
-      <c r="J14" s="32">
+      <c r="H12" s="31">
         <v>104000</v>
       </c>
-      <c r="K14" s="32">
+      <c r="I12" s="31">
         <v>1276375</v>
       </c>
+      <c r="J12" s="31">
+        <v>185000</v>
+      </c>
+      <c r="K12" s="31">
+        <v>100000</v>
+      </c>
+      <c r="L12" s="32">
+        <v>4225375</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="31">
+        <v>25365</v>
+      </c>
+      <c r="C13" s="31">
+        <v>4535</v>
+      </c>
+      <c r="D13" s="31">
+        <v>16889.95</v>
+      </c>
+      <c r="E13" s="31">
+        <v>12811.21</v>
+      </c>
+      <c r="F13" s="31">
+        <v>5742.27</v>
+      </c>
+      <c r="G13" s="31">
+        <v>3005.74</v>
+      </c>
+      <c r="H13" s="31">
+        <v>4358</v>
+      </c>
+      <c r="I13" s="31">
+        <v>10880</v>
+      </c>
+      <c r="J13" s="31">
+        <v>0</v>
+      </c>
+      <c r="K13" s="31">
+        <v>30</v>
+      </c>
+      <c r="L13" s="32">
+        <v>83617.17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="31">
+        <v>4829.95</v>
+      </c>
+      <c r="C14" s="31">
+        <v>22528.39</v>
+      </c>
+      <c r="D14" s="31">
+        <v>22405.94</v>
+      </c>
+      <c r="E14" s="31">
+        <v>5071.17</v>
+      </c>
+      <c r="F14" s="31">
+        <v>20601.38</v>
+      </c>
+      <c r="G14" s="31">
+        <v>34642.92</v>
+      </c>
+      <c r="H14" s="31">
+        <v>25048.400000000001</v>
+      </c>
+      <c r="I14" s="31">
+        <v>32055.17</v>
+      </c>
+      <c r="J14" s="31">
+        <v>0</v>
+      </c>
+      <c r="K14" s="31">
+        <v>0</v>
+      </c>
       <c r="L14" s="32">
-        <v>185000</v>
-      </c>
-      <c r="M14" s="32">
-        <v>100000</v>
-      </c>
-      <c r="N14" s="33">
-        <v>4225375</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="21"/>
-      <c r="C15" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="32">
-        <v>25365</v>
-      </c>
-      <c r="E15" s="32">
-        <v>4535</v>
-      </c>
-      <c r="F15" s="32">
-        <v>16889.95</v>
-      </c>
-      <c r="G15" s="32">
-        <v>12811.21</v>
-      </c>
-      <c r="H15" s="32">
-        <v>5742.27</v>
-      </c>
-      <c r="I15" s="32">
-        <v>3005.74</v>
-      </c>
-      <c r="J15" s="32">
-        <v>4358</v>
-      </c>
-      <c r="K15" s="32">
-        <v>10880</v>
+        <v>167183.32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="31">
+        <v>1768</v>
+      </c>
+      <c r="C15" s="31">
+        <v>1432</v>
+      </c>
+      <c r="D15" s="31">
+        <v>1698</v>
+      </c>
+      <c r="E15" s="31">
+        <v>1255.9100000000001</v>
+      </c>
+      <c r="F15" s="31">
+        <v>505</v>
+      </c>
+      <c r="G15" s="31">
+        <v>525</v>
+      </c>
+      <c r="H15" s="31">
+        <v>749</v>
+      </c>
+      <c r="I15" s="31">
+        <v>5665.25</v>
+      </c>
+      <c r="J15" s="31">
+        <v>0</v>
+      </c>
+      <c r="K15" s="31">
+        <v>0</v>
       </c>
       <c r="L15" s="32">
-        <v>0</v>
-      </c>
-      <c r="M15" s="32">
-        <v>30</v>
-      </c>
-      <c r="N15" s="33">
-        <v>83617.17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="21"/>
-      <c r="C16" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="32">
-        <v>4829.95</v>
-      </c>
-      <c r="E16" s="32">
-        <v>22528.39</v>
-      </c>
-      <c r="F16" s="32">
-        <v>22405.94</v>
-      </c>
-      <c r="G16" s="32">
-        <v>5071.17</v>
-      </c>
-      <c r="H16" s="32">
-        <v>20601.38</v>
-      </c>
-      <c r="I16" s="32">
-        <v>34642.92</v>
-      </c>
-      <c r="J16" s="32">
-        <v>25048.400000000001</v>
-      </c>
-      <c r="K16" s="32">
-        <v>32055.17</v>
+        <v>13598.16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="31">
+        <v>9000</v>
+      </c>
+      <c r="C16" s="31">
+        <v>6900</v>
+      </c>
+      <c r="D16" s="31">
+        <v>21000</v>
+      </c>
+      <c r="E16" s="31">
+        <v>4500</v>
+      </c>
+      <c r="F16" s="31">
+        <v>2100</v>
+      </c>
+      <c r="G16" s="31">
+        <v>12000</v>
+      </c>
+      <c r="H16" s="31">
+        <v>9900</v>
+      </c>
+      <c r="I16" s="31">
+        <v>19250</v>
+      </c>
+      <c r="J16" s="31">
+        <v>0</v>
+      </c>
+      <c r="K16" s="31">
+        <v>0</v>
       </c>
       <c r="L16" s="32">
-        <v>0</v>
-      </c>
-      <c r="M16" s="32">
-        <v>0</v>
-      </c>
-      <c r="N16" s="33">
-        <v>167183.32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="21"/>
-      <c r="C17" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="D17" s="32">
-        <v>1768</v>
-      </c>
-      <c r="E17" s="32">
-        <v>1432</v>
-      </c>
-      <c r="F17" s="32">
-        <v>1698</v>
-      </c>
-      <c r="G17" s="32">
-        <v>1255.9100000000001</v>
-      </c>
-      <c r="H17" s="32">
-        <v>505</v>
-      </c>
-      <c r="I17" s="32">
-        <v>525</v>
-      </c>
-      <c r="J17" s="32">
-        <v>749</v>
-      </c>
-      <c r="K17" s="32">
-        <v>5665.25</v>
-      </c>
-      <c r="L17" s="32">
-        <v>0</v>
-      </c>
-      <c r="M17" s="32">
-        <v>0</v>
-      </c>
-      <c r="N17" s="33">
-        <v>13598.16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="21"/>
-      <c r="C18" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" s="32">
-        <v>9000</v>
-      </c>
-      <c r="E18" s="32">
-        <v>6900</v>
-      </c>
-      <c r="F18" s="32">
-        <v>21000</v>
-      </c>
-      <c r="G18" s="32">
-        <v>4500</v>
-      </c>
-      <c r="H18" s="32">
-        <v>2100</v>
-      </c>
-      <c r="I18" s="32">
-        <v>12000</v>
-      </c>
-      <c r="J18" s="32">
-        <v>9900</v>
-      </c>
-      <c r="K18" s="32">
-        <v>19250</v>
-      </c>
-      <c r="L18" s="32">
-        <v>0</v>
-      </c>
-      <c r="M18" s="32">
-        <v>0</v>
-      </c>
-      <c r="N18" s="33">
         <v>84650</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C19" s="22" t="s">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="D19" s="23">
+      <c r="B17" s="22">
         <v>-148129.95000000001</v>
       </c>
-      <c r="E19" s="23">
+      <c r="C17" s="22">
         <v>-375889.39</v>
       </c>
-      <c r="F19" s="23">
+      <c r="D17" s="22">
         <v>251851.1100000001</v>
       </c>
-      <c r="G19" s="23">
+      <c r="E17" s="22">
         <v>-31520.290000000008</v>
       </c>
-      <c r="H19" s="23">
+      <c r="F17" s="22">
         <v>91508.35</v>
       </c>
-      <c r="I19" s="23">
+      <c r="G17" s="22">
         <v>-188739.66000000003</v>
       </c>
-      <c r="J19" s="23">
+      <c r="H17" s="22">
         <v>23607.600000000006</v>
       </c>
-      <c r="K19" s="23">
+      <c r="I17" s="22">
         <v>732875.58000000007</v>
       </c>
-      <c r="L19" s="23">
+      <c r="J17" s="22">
         <v>-87000</v>
       </c>
-      <c r="M19" s="23">
+      <c r="K17" s="22">
         <v>40837</v>
       </c>
-      <c r="N19" s="24">
+      <c r="L17" s="23">
         <v>309400.35000000009</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C20" s="34" t="s">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="35">
+      <c r="B18" s="34">
         <v>-0.61000749486272465</v>
       </c>
-      <c r="E20" s="35">
+      <c r="C18" s="34">
         <v>-1.7941700476358673</v>
       </c>
-      <c r="F20" s="35">
+      <c r="D18" s="34">
         <v>0.23673665806578975</v>
       </c>
-      <c r="G20" s="35">
+      <c r="E18" s="34">
         <v>-0.1640673440281494</v>
       </c>
-      <c r="H20" s="35">
+      <c r="F18" s="34">
         <v>0.28555578439541035</v>
       </c>
-      <c r="I20" s="35">
+      <c r="G18" s="34">
         <v>-0.50813781183198103</v>
       </c>
-      <c r="J20" s="35">
+      <c r="H18" s="34">
         <v>0.14080387443860604</v>
       </c>
-      <c r="K20" s="35">
+      <c r="I18" s="34">
         <v>0.35283579373367019</v>
       </c>
-      <c r="L20" s="35">
+      <c r="J18" s="34">
         <v>-0.88775510204081631</v>
       </c>
-      <c r="M20" s="35">
+      <c r="K18" s="34">
         <v>0.28989756294944879</v>
       </c>
-      <c r="N20" s="36">
+      <c r="L18" s="35">
         <v>6.3352067969689341E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C21" s="25"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="26"/>
-      <c r="J21" s="26"/>
-      <c r="K21" s="26"/>
-      <c r="L21" s="26"/>
-      <c r="M21" s="26"/>
-      <c r="N21" s="27"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="21"/>
-      <c r="C22" s="31" t="s">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="24"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="25"/>
+      <c r="K19" s="25"/>
+      <c r="L19" s="26"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="D22" s="32">
-        <v>0</v>
-      </c>
-      <c r="E22" s="32">
-        <v>0</v>
-      </c>
-      <c r="F22" s="32">
+      <c r="B20" s="31">
+        <v>0</v>
+      </c>
+      <c r="C20" s="31">
+        <v>0</v>
+      </c>
+      <c r="D20" s="31">
         <v>9617.74</v>
       </c>
-      <c r="G22" s="32">
-        <v>0</v>
-      </c>
-      <c r="H22" s="32">
-        <v>0</v>
-      </c>
-      <c r="I22" s="32">
-        <v>0</v>
-      </c>
-      <c r="J22" s="32">
-        <v>0</v>
-      </c>
-      <c r="K22" s="32">
-        <v>0</v>
-      </c>
-      <c r="L22" s="32">
-        <v>0</v>
-      </c>
-      <c r="M22" s="32">
-        <v>0</v>
-      </c>
-      <c r="N22" s="30">
+      <c r="E20" s="31">
+        <v>0</v>
+      </c>
+      <c r="F20" s="31">
+        <v>0</v>
+      </c>
+      <c r="G20" s="31">
+        <v>0</v>
+      </c>
+      <c r="H20" s="31">
+        <v>0</v>
+      </c>
+      <c r="I20" s="31">
+        <v>0</v>
+      </c>
+      <c r="J20" s="31">
+        <v>0</v>
+      </c>
+      <c r="K20" s="31">
+        <v>0</v>
+      </c>
+      <c r="L20" s="29">
         <v>9617.74</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C23" s="22" t="s">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="D23" s="23">
+      <c r="B21" s="22">
         <v>-148129.95000000001</v>
       </c>
-      <c r="E23" s="23">
+      <c r="C21" s="22">
         <v>-375889.39</v>
       </c>
-      <c r="F23" s="23">
+      <c r="D21" s="22">
         <v>242233.37000000011</v>
       </c>
-      <c r="G23" s="23">
+      <c r="E21" s="22">
         <v>-31520.290000000008</v>
       </c>
-      <c r="H23" s="23">
+      <c r="F21" s="22">
         <v>91508.35</v>
       </c>
-      <c r="I23" s="23">
+      <c r="G21" s="22">
         <v>-188739.66000000003</v>
       </c>
-      <c r="J23" s="23">
+      <c r="H21" s="22">
         <v>23607.600000000006</v>
       </c>
-      <c r="K23" s="23">
+      <c r="I21" s="22">
         <v>732875.58000000007</v>
       </c>
-      <c r="L23" s="23">
+      <c r="J21" s="22">
         <v>-87000</v>
       </c>
-      <c r="M23" s="23">
+      <c r="K21" s="22">
         <v>40837</v>
       </c>
-      <c r="N23" s="24">
+      <c r="L21" s="23">
         <v>299782.6100000001</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C24" s="34" t="s">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="D24" s="35">
+      <c r="B22" s="34">
         <v>-0.61000749486272465</v>
       </c>
-      <c r="E24" s="35">
+      <c r="C22" s="34">
         <v>-1.7941700476358673</v>
       </c>
-      <c r="F24" s="35">
+      <c r="D22" s="34">
         <v>0.22769611174560214</v>
       </c>
-      <c r="G24" s="35">
+      <c r="E22" s="34">
         <v>-0.1640673440281494</v>
       </c>
-      <c r="H24" s="35">
+      <c r="F22" s="34">
         <v>0.28555578439541035</v>
       </c>
-      <c r="I24" s="35">
+      <c r="G22" s="34">
         <v>-0.50813781183198103</v>
       </c>
-      <c r="J24" s="35">
+      <c r="H22" s="34">
         <v>0.14080387443860604</v>
       </c>
-      <c r="K24" s="35">
+      <c r="I22" s="34">
         <v>0.35283579373367019</v>
       </c>
-      <c r="L24" s="35">
+      <c r="J22" s="34">
         <v>-0.88775510204081631</v>
       </c>
-      <c r="M24" s="35">
+      <c r="K22" s="34">
         <v>0.28989756294944879</v>
       </c>
-      <c r="N24" s="36">
+      <c r="L22" s="35">
         <v>6.1382762769501956E-2</v>
       </c>
     </row>

--- a/P&L_Rent_Projects_F.xlsx
+++ b/P&L_Rent_Projects_F.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\سدرة الخير\Hub Project Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E334EEC1-2E13-4689-A15C-868AD277EFB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1362F0C-A4C4-4CCA-8364-8B34BBA2C80C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{D8720DA4-03DD-471F-8DC0-E7471CF99247}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
   <si>
     <t>ايجار الملقا</t>
   </si>
@@ -75,9 +75,6 @@
     <t>Net Revenue</t>
   </si>
   <si>
-    <t>2. OPERATING EXPENSES</t>
-  </si>
-  <si>
     <t>Total OPEX</t>
   </si>
   <si>
@@ -102,26 +99,28 @@
     <t>Operating Income Margin (%)</t>
   </si>
   <si>
-    <t>Leasehold Improvements Amortization</t>
-  </si>
-  <si>
     <t>Net Profit</t>
   </si>
   <si>
     <t>Net Profit Margin (%)</t>
+  </si>
+  <si>
+    <t>Improvements Amortization</t>
+  </si>
+  <si>
+    <t>Category</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* \-??_);_(@_)"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -192,14 +191,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF1F4E78"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -237,7 +228,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -274,14 +265,8 @@
         <bgColor rgb="FFD9EAF7"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFF3F6F9"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="18">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -412,17 +397,6 @@
       <right style="thin">
         <color theme="0" tint="-4.9989318521683403E-2"/>
       </right>
-      <top style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </left>
-      <right/>
       <top style="thin">
         <color theme="0" tint="-4.9989318521683403E-2"/>
       </top>
@@ -460,36 +434,29 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFD9E1F2"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
+      <left style="thin">
         <color rgb="FFD9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+      </left>
       <right style="thin">
         <color rgb="FFD9D9D9"/>
       </right>
       <top style="thin">
         <color rgb="FFD9D9D9"/>
       </top>
-      <bottom style="thin">
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFD9D9D9"/>
-      </bottom>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9E1F2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -499,7 +466,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -513,58 +480,53 @@
     <xf numFmtId="49" fontId="5" fillId="3" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="3" fillId="4" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="3" fillId="4" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="3" fillId="4" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="3" fillId="4" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="6" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="3" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -572,7 +534,530 @@
     <cellStyle name="Normal 3" xfId="3" xr:uid="{BCDE9B6F-D371-4E11-8F30-4B0D6DE6CDCA}"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="16">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="8"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="8"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.499984740745262"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -583,6 +1068,50 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0C617C18-5DD5-4293-ADEF-12A3AF245BA7}" name="occupancy" displayName="occupancy" ref="A1:L5" totalsRowShown="0" headerRowDxfId="3" dataDxfId="4" headerRowCellStyle="Normal 3" dataCellStyle="Percent">
+  <autoFilter ref="A1:L5" xr:uid="{0C617C18-5DD5-4293-ADEF-12A3AF245BA7}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{9BB78B6B-9017-48AA-907B-DFFBE122E04A}" name="Category" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{3A542653-2853-408C-BAC8-A8CA1862B2D4}" name="ايجار الملقا" dataDxfId="14" dataCellStyle="Percent"/>
+    <tableColumn id="3" xr3:uid="{147B61C1-F613-43BC-AF01-82B8496D1BCC}" name="ايجار النرجس" dataDxfId="13" dataCellStyle="Percent"/>
+    <tableColumn id="4" xr3:uid="{778AD9A3-6658-41D2-9B96-0AA545212064}" name="ايجار المرسلات" dataDxfId="12" dataCellStyle="Percent"/>
+    <tableColumn id="5" xr3:uid="{B30B15DA-6802-4366-8546-6A76B5DD1E93}" name="ايجار النزهة" dataDxfId="11" dataCellStyle="Percent"/>
+    <tableColumn id="6" xr3:uid="{2F259610-B550-4920-BBE2-E8F63FB1FF2E}" name="ايجار الياسمين" dataDxfId="10" dataCellStyle="Percent"/>
+    <tableColumn id="7" xr3:uid="{00EFD7BC-116E-4306-8BBE-CCC40483E33C}" name="ايجار الدرعية" dataDxfId="9" dataCellStyle="Percent"/>
+    <tableColumn id="8" xr3:uid="{56F2FCA3-EB77-439C-9CC5-D178F54956F6}" name="ايجار السويدى" dataDxfId="8" dataCellStyle="Percent"/>
+    <tableColumn id="9" xr3:uid="{B31C8387-A17D-4FEF-983A-61F89E1659C8}" name="ايجار العارض" dataDxfId="7" dataCellStyle="Percent"/>
+    <tableColumn id="10" xr3:uid="{718E92B1-415F-4DFF-A1DC-D438DB02E139}" name="فيلا الندي" dataDxfId="6" dataCellStyle="Percent"/>
+    <tableColumn id="11" xr3:uid="{6F7F5C6F-DC4C-4031-8C03-7CA779183D65}" name="فيلا النزهة" dataDxfId="5" dataCellStyle="Percent"/>
+    <tableColumn id="12" xr3:uid="{F86F566A-5358-4455-8AD8-8FBC68C89943}" name="TOTAL" dataDxfId="2">
+      <calculatedColumnFormula>AVERAGE(occupancy[[#This Row],[ايجار الملقا]:[فيلا النزهة]])</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D5BE1C88-1721-4CC7-96C5-0F260C35304A}" name="rent_P_L" displayName="rent_P_L" ref="A7:L19" totalsRowShown="0" headerRowDxfId="0" tableBorderDxfId="1" headerRowCellStyle="Normal 3">
+  <autoFilter ref="A7:L19" xr:uid="{D5BE1C88-1721-4CC7-96C5-0F260C35304A}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{9DF92254-83EE-43C7-AC1B-55C1C06C8B9E}" name="Category"/>
+    <tableColumn id="2" xr3:uid="{3E74B3FC-419A-4E48-B546-7DB4EB79C8D3}" name="ايجار الملقا"/>
+    <tableColumn id="3" xr3:uid="{2955034E-D833-4A35-BD0D-DD3F8550C9B6}" name="ايجار النرجس"/>
+    <tableColumn id="4" xr3:uid="{23C6316A-4EC8-44D4-9B9E-B67497EBF825}" name="ايجار المرسلات"/>
+    <tableColumn id="5" xr3:uid="{781FD08F-8D60-40D7-A795-6858AAFCD912}" name="ايجار النزهة"/>
+    <tableColumn id="6" xr3:uid="{6D2BDFE0-CF7A-45E2-9E80-DD6CDDDA2964}" name="ايجار الياسمين"/>
+    <tableColumn id="7" xr3:uid="{C33A115B-4BD3-4DE7-B737-84D3B78999F3}" name="ايجار الدرعية"/>
+    <tableColumn id="8" xr3:uid="{B589ED5F-DB97-4D52-B3C9-A62CD58D72EB}" name="ايجار السويدى"/>
+    <tableColumn id="9" xr3:uid="{C397D10B-BDE3-41B9-B4F8-B88506F963B9}" name="ايجار العارض"/>
+    <tableColumn id="10" xr3:uid="{88E74039-1D5E-45A5-B638-D41A606D731C}" name="فيلا الندي"/>
+    <tableColumn id="11" xr3:uid="{A53F79E4-5499-489D-A6AB-901F228BBF99}" name="فيلا النزهة"/>
+    <tableColumn id="12" xr3:uid="{778100A9-529E-48EC-8100-14236ECE0E3A}" name="TOTAL"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -882,15 +1411,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3488CD7C-8A5C-4EE4-8C4C-F7117492D1F2}">
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36.44140625" customWidth="1"/>
-    <col min="2" max="11" width="12.77734375" customWidth="1"/>
+    <col min="2" max="3" width="12.77734375" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="11" width="12.77734375" customWidth="1"/>
     <col min="12" max="12" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
@@ -926,671 +1460,660 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="5"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="7"/>
+      <c r="A2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="6">
+        <v>13</v>
+      </c>
+      <c r="C2" s="7">
+        <v>28</v>
+      </c>
+      <c r="D2" s="7">
+        <v>41</v>
+      </c>
+      <c r="E2" s="7">
+        <v>18</v>
+      </c>
+      <c r="F2" s="7">
+        <v>31</v>
+      </c>
+      <c r="G2" s="7">
+        <v>48</v>
+      </c>
+      <c r="H2" s="7">
+        <v>9</v>
+      </c>
+      <c r="I2" s="7">
+        <v>51</v>
+      </c>
+      <c r="J2" s="7">
+        <v>10</v>
+      </c>
+      <c r="K2" s="7">
+        <v>14</v>
+      </c>
+      <c r="L2" s="27">
+        <f>SUM(occupancy[[#This Row],[ايجار الملقا]:[فيلا النزهة]])</f>
+        <v>263</v>
+      </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="9">
-        <v>13</v>
-      </c>
-      <c r="C3" s="10">
-        <v>28</v>
-      </c>
-      <c r="D3" s="10">
-        <v>41</v>
-      </c>
-      <c r="E3" s="10">
+      <c r="A3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="8">
+        <v>8</v>
+      </c>
+      <c r="C3" s="9">
+        <v>22</v>
+      </c>
+      <c r="D3" s="9">
+        <v>34</v>
+      </c>
+      <c r="E3" s="9">
         <v>18</v>
       </c>
-      <c r="F3" s="10">
-        <v>31</v>
-      </c>
-      <c r="G3" s="10">
+      <c r="F3" s="9">
+        <v>30</v>
+      </c>
+      <c r="G3" s="9">
         <v>48</v>
       </c>
-      <c r="H3" s="10">
+      <c r="H3" s="9">
+        <v>7</v>
+      </c>
+      <c r="I3" s="9">
+        <v>51</v>
+      </c>
+      <c r="J3" s="9">
         <v>9</v>
       </c>
-      <c r="I3" s="10">
-        <v>51</v>
-      </c>
-      <c r="J3" s="10">
-        <v>10</v>
-      </c>
-      <c r="K3" s="10">
+      <c r="K3" s="9">
         <v>14</v>
       </c>
-      <c r="L3" s="11">
-        <v>263</v>
+      <c r="L3" s="27">
+        <f>SUM(occupancy[[#This Row],[ايجار الملقا]:[فيلا النزهة]])</f>
+        <v>241</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="12">
-        <v>8</v>
-      </c>
-      <c r="C4" s="13">
-        <v>22</v>
-      </c>
-      <c r="D4" s="13">
-        <v>34</v>
-      </c>
-      <c r="E4" s="13">
-        <v>18</v>
-      </c>
-      <c r="F4" s="13">
-        <v>30</v>
-      </c>
-      <c r="G4" s="13">
-        <v>48</v>
-      </c>
-      <c r="H4" s="13">
-        <v>7</v>
-      </c>
-      <c r="I4" s="13">
-        <v>51</v>
-      </c>
-      <c r="J4" s="13">
-        <v>9</v>
-      </c>
-      <c r="K4" s="13">
-        <v>14</v>
-      </c>
-      <c r="L4" s="14">
-        <v>241</v>
+      <c r="A4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="10">
+        <v>0.61538461538461542</v>
+      </c>
+      <c r="C4" s="11">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="D4" s="11">
+        <v>0.82926829268292679</v>
+      </c>
+      <c r="E4" s="11">
+        <v>1</v>
+      </c>
+      <c r="F4" s="11">
+        <v>0.967741935483871</v>
+      </c>
+      <c r="G4" s="11">
+        <v>1</v>
+      </c>
+      <c r="H4" s="11">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="I4" s="11">
+        <v>1</v>
+      </c>
+      <c r="J4" s="11">
+        <v>0.9</v>
+      </c>
+      <c r="K4" s="11">
+        <v>1</v>
+      </c>
+      <c r="L4" s="12">
+        <f>AVERAGE(occupancy[[#This Row],[ايجار الملقا]:[فيلا النزهة]])</f>
+        <v>0.88758869070434765</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="15">
-        <v>0.61538461538461542</v>
-      </c>
-      <c r="C5" s="16">
-        <v>0.7857142857142857</v>
-      </c>
-      <c r="D5" s="16">
-        <v>0.82926829268292679</v>
-      </c>
-      <c r="E5" s="16">
+      <c r="A5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="13">
+        <v>263984.25</v>
+      </c>
+      <c r="C5" s="14">
+        <v>1053228.27</v>
+      </c>
+      <c r="D5" s="14">
+        <v>563328.69999999995</v>
+      </c>
+      <c r="E5" s="14">
+        <v>876392.56</v>
+      </c>
+      <c r="F5" s="14">
+        <v>300146.36</v>
+      </c>
+      <c r="G5" s="14">
+        <v>250000</v>
+      </c>
+      <c r="H5" s="14">
+        <v>220379.96</v>
+      </c>
+      <c r="I5" s="14">
+        <v>716213.33000000007</v>
+      </c>
+      <c r="J5" s="14">
+        <v>335924.65</v>
+      </c>
+      <c r="K5" s="14">
+        <v>654450.31999999995</v>
+      </c>
+      <c r="L5" s="28">
+        <f>SUM(occupancy[[#This Row],[ايجار الملقا]:[فيلا النزهة]])</f>
+        <v>5234048.4000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="16">
-        <v>0.967741935483871</v>
-      </c>
-      <c r="G5" s="16">
-        <v>1</v>
-      </c>
-      <c r="H5" s="16">
-        <v>0.77777777777777779</v>
-      </c>
-      <c r="I5" s="16">
-        <v>1</v>
-      </c>
-      <c r="J5" s="16">
-        <v>0.9</v>
-      </c>
-      <c r="K5" s="16">
-        <v>1</v>
-      </c>
-      <c r="L5" s="17">
-        <v>0.91634980988593151</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="18">
-        <v>263984.25</v>
-      </c>
-      <c r="C6" s="19">
-        <v>1053228.27</v>
-      </c>
-      <c r="D6" s="19">
-        <v>563328.69999999995</v>
-      </c>
-      <c r="E6" s="19">
-        <v>876392.56</v>
-      </c>
-      <c r="F6" s="19">
-        <v>300146.36</v>
-      </c>
-      <c r="G6" s="19">
-        <v>250000</v>
-      </c>
-      <c r="H6" s="19">
-        <v>220379.96</v>
-      </c>
-      <c r="I6" s="19">
-        <v>716213.33000000007</v>
-      </c>
-      <c r="J6" s="19">
-        <v>335924.65</v>
-      </c>
-      <c r="K6" s="19">
-        <v>654450.31999999995</v>
-      </c>
-      <c r="L6" s="20">
-        <v>5234048.4000000004</v>
+      <c r="D7" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="22">
+      <c r="B8" s="16">
         <v>242833</v>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="16">
         <v>209506</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="16">
         <v>1063845</v>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="16">
         <v>192118</v>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="16">
         <v>320457</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="16">
         <v>371434</v>
       </c>
-      <c r="H8" s="22">
+      <c r="H8" s="16">
         <v>167663</v>
       </c>
-      <c r="I8" s="22">
+      <c r="I8" s="16">
         <v>2077101</v>
       </c>
-      <c r="J8" s="22">
+      <c r="J8" s="16">
         <v>98000</v>
       </c>
-      <c r="K8" s="22">
+      <c r="K8" s="16">
         <v>140867</v>
       </c>
-      <c r="L8" s="23">
+      <c r="L8" s="17">
         <v>4883824</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="24"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="25"/>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="26"/>
+      <c r="A9" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="22">
+        <v>350000</v>
+      </c>
+      <c r="C9" s="22">
+        <v>550000</v>
+      </c>
+      <c r="D9" s="22">
+        <v>750000</v>
+      </c>
+      <c r="E9" s="22">
+        <v>200000</v>
+      </c>
+      <c r="F9" s="22">
+        <v>200000</v>
+      </c>
+      <c r="G9" s="22">
+        <v>510000</v>
+      </c>
+      <c r="H9" s="22">
+        <v>104000</v>
+      </c>
+      <c r="I9" s="22">
+        <v>1276375</v>
+      </c>
+      <c r="J9" s="22">
+        <v>185000</v>
+      </c>
+      <c r="K9" s="22">
+        <v>100000</v>
+      </c>
+      <c r="L9" s="23">
+        <v>4225375</v>
+      </c>
     </row>
-    <row r="10" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="37"/>
-      <c r="C10" s="37"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="37"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="37"/>
-      <c r="J10" s="37"/>
-      <c r="K10" s="37"/>
-      <c r="L10" s="38"/>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="22">
+        <v>25365</v>
+      </c>
+      <c r="C10" s="22">
+        <v>4535</v>
+      </c>
+      <c r="D10" s="22">
+        <v>16889.95</v>
+      </c>
+      <c r="E10" s="22">
+        <v>12811.21</v>
+      </c>
+      <c r="F10" s="22">
+        <v>5742.27</v>
+      </c>
+      <c r="G10" s="22">
+        <v>3005.74</v>
+      </c>
+      <c r="H10" s="22">
+        <v>4358</v>
+      </c>
+      <c r="I10" s="22">
+        <v>10880</v>
+      </c>
+      <c r="J10" s="22">
+        <v>0</v>
+      </c>
+      <c r="K10" s="22">
+        <v>30</v>
+      </c>
+      <c r="L10" s="23">
+        <v>83617.17</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="28">
-        <v>390962.95</v>
-      </c>
-      <c r="C11" s="28">
-        <v>585395.39</v>
-      </c>
-      <c r="D11" s="28">
-        <v>811993.8899999999</v>
-      </c>
-      <c r="E11" s="28">
-        <v>223638.29</v>
-      </c>
-      <c r="F11" s="28">
-        <v>228948.65</v>
-      </c>
-      <c r="G11" s="28">
-        <v>560173.66</v>
-      </c>
-      <c r="H11" s="28">
-        <v>144055.4</v>
-      </c>
-      <c r="I11" s="28">
-        <v>1344225.42</v>
-      </c>
-      <c r="J11" s="28">
-        <v>185000</v>
-      </c>
-      <c r="K11" s="28">
-        <v>100030</v>
-      </c>
-      <c r="L11" s="29">
-        <v>4574423.6500000004</v>
+      <c r="A11" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="22">
+        <v>4829.95</v>
+      </c>
+      <c r="C11" s="22">
+        <v>22528.39</v>
+      </c>
+      <c r="D11" s="22">
+        <v>22405.94</v>
+      </c>
+      <c r="E11" s="22">
+        <v>5071.17</v>
+      </c>
+      <c r="F11" s="22">
+        <v>20601.38</v>
+      </c>
+      <c r="G11" s="22">
+        <v>34642.92</v>
+      </c>
+      <c r="H11" s="22">
+        <v>25048.400000000001</v>
+      </c>
+      <c r="I11" s="22">
+        <v>32055.17</v>
+      </c>
+      <c r="J11" s="22">
+        <v>0</v>
+      </c>
+      <c r="K11" s="22">
+        <v>0</v>
+      </c>
+      <c r="L11" s="23">
+        <v>167183.32</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="31">
-        <v>350000</v>
-      </c>
-      <c r="C12" s="31">
-        <v>550000</v>
-      </c>
-      <c r="D12" s="31">
-        <v>750000</v>
-      </c>
-      <c r="E12" s="31">
-        <v>200000</v>
-      </c>
-      <c r="F12" s="31">
-        <v>200000</v>
-      </c>
-      <c r="G12" s="31">
-        <v>510000</v>
-      </c>
-      <c r="H12" s="31">
-        <v>104000</v>
-      </c>
-      <c r="I12" s="31">
-        <v>1276375</v>
-      </c>
-      <c r="J12" s="31">
-        <v>185000</v>
-      </c>
-      <c r="K12" s="31">
-        <v>100000</v>
-      </c>
-      <c r="L12" s="32">
-        <v>4225375</v>
+      <c r="A12" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="22">
+        <v>1768</v>
+      </c>
+      <c r="C12" s="22">
+        <v>1432</v>
+      </c>
+      <c r="D12" s="22">
+        <v>1698</v>
+      </c>
+      <c r="E12" s="22">
+        <v>1255.9100000000001</v>
+      </c>
+      <c r="F12" s="22">
+        <v>505</v>
+      </c>
+      <c r="G12" s="22">
+        <v>525</v>
+      </c>
+      <c r="H12" s="22">
+        <v>749</v>
+      </c>
+      <c r="I12" s="22">
+        <v>5665.25</v>
+      </c>
+      <c r="J12" s="22">
+        <v>0</v>
+      </c>
+      <c r="K12" s="22">
+        <v>0</v>
+      </c>
+      <c r="L12" s="23">
+        <v>13598.16</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="31">
-        <v>25365</v>
-      </c>
-      <c r="C13" s="31">
-        <v>4535</v>
-      </c>
-      <c r="D13" s="31">
-        <v>16889.95</v>
-      </c>
-      <c r="E13" s="31">
-        <v>12811.21</v>
-      </c>
-      <c r="F13" s="31">
-        <v>5742.27</v>
-      </c>
-      <c r="G13" s="31">
-        <v>3005.74</v>
-      </c>
-      <c r="H13" s="31">
-        <v>4358</v>
-      </c>
-      <c r="I13" s="31">
-        <v>10880</v>
-      </c>
-      <c r="J13" s="31">
+      <c r="A13" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="22">
+        <v>9000</v>
+      </c>
+      <c r="C13" s="22">
+        <v>6900</v>
+      </c>
+      <c r="D13" s="22">
+        <v>21000</v>
+      </c>
+      <c r="E13" s="22">
+        <v>4500</v>
+      </c>
+      <c r="F13" s="22">
+        <v>2100</v>
+      </c>
+      <c r="G13" s="22">
+        <v>12000</v>
+      </c>
+      <c r="H13" s="22">
+        <v>9900</v>
+      </c>
+      <c r="I13" s="22">
+        <v>19250</v>
+      </c>
+      <c r="J13" s="22">
         <v>0</v>
       </c>
-      <c r="K13" s="31">
-        <v>30</v>
-      </c>
-      <c r="L13" s="32">
-        <v>83617.17</v>
+      <c r="K13" s="22">
+        <v>0</v>
+      </c>
+      <c r="L13" s="23">
+        <v>84650</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="31">
-        <v>4829.95</v>
-      </c>
-      <c r="C14" s="31">
-        <v>22528.39</v>
-      </c>
-      <c r="D14" s="31">
-        <v>22405.94</v>
-      </c>
-      <c r="E14" s="31">
-        <v>5071.17</v>
-      </c>
-      <c r="F14" s="31">
-        <v>20601.38</v>
-      </c>
-      <c r="G14" s="31">
-        <v>34642.92</v>
-      </c>
-      <c r="H14" s="31">
-        <v>25048.400000000001</v>
-      </c>
-      <c r="I14" s="31">
-        <v>32055.17</v>
-      </c>
-      <c r="J14" s="31">
-        <v>0</v>
-      </c>
-      <c r="K14" s="31">
-        <v>0</v>
-      </c>
-      <c r="L14" s="32">
-        <v>167183.32</v>
+      <c r="A14" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="19">
+        <v>390962.95</v>
+      </c>
+      <c r="C14" s="19">
+        <v>585395.39</v>
+      </c>
+      <c r="D14" s="19">
+        <v>811993.8899999999</v>
+      </c>
+      <c r="E14" s="19">
+        <v>223638.29</v>
+      </c>
+      <c r="F14" s="19">
+        <v>228948.65</v>
+      </c>
+      <c r="G14" s="19">
+        <v>560173.66</v>
+      </c>
+      <c r="H14" s="19">
+        <v>144055.4</v>
+      </c>
+      <c r="I14" s="19">
+        <v>1344225.42</v>
+      </c>
+      <c r="J14" s="19">
+        <v>185000</v>
+      </c>
+      <c r="K14" s="19">
+        <v>100030</v>
+      </c>
+      <c r="L14" s="20">
+        <v>4574423.6500000004</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="31">
-        <v>1768</v>
-      </c>
-      <c r="C15" s="31">
-        <v>1432</v>
-      </c>
-      <c r="D15" s="31">
-        <v>1698</v>
-      </c>
-      <c r="E15" s="31">
-        <v>1255.9100000000001</v>
-      </c>
-      <c r="F15" s="31">
-        <v>505</v>
-      </c>
-      <c r="G15" s="31">
-        <v>525</v>
-      </c>
-      <c r="H15" s="31">
-        <v>749</v>
-      </c>
-      <c r="I15" s="31">
-        <v>5665.25</v>
-      </c>
-      <c r="J15" s="31">
-        <v>0</v>
-      </c>
-      <c r="K15" s="31">
-        <v>0</v>
-      </c>
-      <c r="L15" s="32">
-        <v>13598.16</v>
+      <c r="A15" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="16">
+        <v>-148129.95000000001</v>
+      </c>
+      <c r="C15" s="16">
+        <v>-375889.39</v>
+      </c>
+      <c r="D15" s="16">
+        <v>251851.1100000001</v>
+      </c>
+      <c r="E15" s="16">
+        <v>-31520.290000000008</v>
+      </c>
+      <c r="F15" s="16">
+        <v>91508.35</v>
+      </c>
+      <c r="G15" s="16">
+        <v>-188739.66000000003</v>
+      </c>
+      <c r="H15" s="16">
+        <v>23607.600000000006</v>
+      </c>
+      <c r="I15" s="16">
+        <v>732875.58000000007</v>
+      </c>
+      <c r="J15" s="16">
+        <v>-87000</v>
+      </c>
+      <c r="K15" s="16">
+        <v>40837</v>
+      </c>
+      <c r="L15" s="17">
+        <v>309400.35000000009</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" s="31">
-        <v>9000</v>
-      </c>
-      <c r="C16" s="31">
-        <v>6900</v>
-      </c>
-      <c r="D16" s="31">
-        <v>21000</v>
-      </c>
-      <c r="E16" s="31">
-        <v>4500</v>
-      </c>
-      <c r="F16" s="31">
-        <v>2100</v>
-      </c>
-      <c r="G16" s="31">
-        <v>12000</v>
-      </c>
-      <c r="H16" s="31">
-        <v>9900</v>
-      </c>
-      <c r="I16" s="31">
-        <v>19250</v>
-      </c>
-      <c r="J16" s="31">
-        <v>0</v>
-      </c>
-      <c r="K16" s="31">
-        <v>0</v>
-      </c>
-      <c r="L16" s="32">
-        <v>84650</v>
+      <c r="A16" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="25">
+        <v>-0.61000749486272465</v>
+      </c>
+      <c r="C16" s="25">
+        <v>-1.7941700476358673</v>
+      </c>
+      <c r="D16" s="25">
+        <v>0.23673665806578975</v>
+      </c>
+      <c r="E16" s="25">
+        <v>-0.1640673440281494</v>
+      </c>
+      <c r="F16" s="25">
+        <v>0.28555578439541035</v>
+      </c>
+      <c r="G16" s="25">
+        <v>-0.50813781183198103</v>
+      </c>
+      <c r="H16" s="25">
+        <v>0.14080387443860604</v>
+      </c>
+      <c r="I16" s="25">
+        <v>0.35283579373367019</v>
+      </c>
+      <c r="J16" s="25">
+        <v>-0.88775510204081631</v>
+      </c>
+      <c r="K16" s="25">
+        <v>0.28989756294944879</v>
+      </c>
+      <c r="L16" s="26">
+        <v>6.3352067969689341E-2</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="21" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B17" s="22">
-        <v>-148129.95000000001</v>
+        <v>0</v>
       </c>
       <c r="C17" s="22">
-        <v>-375889.39</v>
+        <v>0</v>
       </c>
       <c r="D17" s="22">
-        <v>251851.1100000001</v>
+        <v>9617.74</v>
       </c>
       <c r="E17" s="22">
-        <v>-31520.290000000008</v>
+        <v>0</v>
       </c>
       <c r="F17" s="22">
-        <v>91508.35</v>
+        <v>0</v>
       </c>
       <c r="G17" s="22">
-        <v>-188739.66000000003</v>
+        <v>0</v>
       </c>
       <c r="H17" s="22">
-        <v>23607.600000000006</v>
+        <v>0</v>
       </c>
       <c r="I17" s="22">
-        <v>732875.58000000007</v>
+        <v>0</v>
       </c>
       <c r="J17" s="22">
-        <v>-87000</v>
+        <v>0</v>
       </c>
       <c r="K17" s="22">
-        <v>40837</v>
-      </c>
-      <c r="L17" s="23">
-        <v>309400.35000000009</v>
+        <v>0</v>
+      </c>
+      <c r="L17" s="20">
+        <v>9617.74</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="33" t="s">
+      <c r="A18" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="34">
-        <v>-0.61000749486272465</v>
-      </c>
-      <c r="C18" s="34">
-        <v>-1.7941700476358673</v>
-      </c>
-      <c r="D18" s="34">
-        <v>0.23673665806578975</v>
-      </c>
-      <c r="E18" s="34">
-        <v>-0.1640673440281494</v>
-      </c>
-      <c r="F18" s="34">
-        <v>0.28555578439541035</v>
-      </c>
-      <c r="G18" s="34">
-        <v>-0.50813781183198103</v>
-      </c>
-      <c r="H18" s="34">
-        <v>0.14080387443860604</v>
-      </c>
-      <c r="I18" s="34">
-        <v>0.35283579373367019</v>
-      </c>
-      <c r="J18" s="34">
-        <v>-0.88775510204081631</v>
-      </c>
-      <c r="K18" s="34">
-        <v>0.28989756294944879</v>
-      </c>
-      <c r="L18" s="35">
-        <v>6.3352067969689341E-2</v>
+      <c r="B18" s="16">
+        <v>-148129.95000000001</v>
+      </c>
+      <c r="C18" s="16">
+        <v>-375889.39</v>
+      </c>
+      <c r="D18" s="16">
+        <v>242233.37000000011</v>
+      </c>
+      <c r="E18" s="16">
+        <v>-31520.290000000008</v>
+      </c>
+      <c r="F18" s="16">
+        <v>91508.35</v>
+      </c>
+      <c r="G18" s="16">
+        <v>-188739.66000000003</v>
+      </c>
+      <c r="H18" s="16">
+        <v>23607.600000000006</v>
+      </c>
+      <c r="I18" s="16">
+        <v>732875.58000000007</v>
+      </c>
+      <c r="J18" s="16">
+        <v>-87000</v>
+      </c>
+      <c r="K18" s="16">
+        <v>40837</v>
+      </c>
+      <c r="L18" s="17">
+        <v>299782.6100000001</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="24"/>
-      <c r="B19" s="25"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="25"/>
-      <c r="I19" s="25"/>
-      <c r="J19" s="25"/>
-      <c r="K19" s="25"/>
-      <c r="L19" s="26"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="30" t="s">
+      <c r="A19" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="31">
-        <v>0</v>
-      </c>
-      <c r="C20" s="31">
-        <v>0</v>
-      </c>
-      <c r="D20" s="31">
-        <v>9617.74</v>
-      </c>
-      <c r="E20" s="31">
-        <v>0</v>
-      </c>
-      <c r="F20" s="31">
-        <v>0</v>
-      </c>
-      <c r="G20" s="31">
-        <v>0</v>
-      </c>
-      <c r="H20" s="31">
-        <v>0</v>
-      </c>
-      <c r="I20" s="31">
-        <v>0</v>
-      </c>
-      <c r="J20" s="31">
-        <v>0</v>
-      </c>
-      <c r="K20" s="31">
-        <v>0</v>
-      </c>
-      <c r="L20" s="29">
-        <v>9617.74</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="22">
-        <v>-148129.95000000001</v>
-      </c>
-      <c r="C21" s="22">
-        <v>-375889.39</v>
-      </c>
-      <c r="D21" s="22">
-        <v>242233.37000000011</v>
-      </c>
-      <c r="E21" s="22">
-        <v>-31520.290000000008</v>
-      </c>
-      <c r="F21" s="22">
-        <v>91508.35</v>
-      </c>
-      <c r="G21" s="22">
-        <v>-188739.66000000003</v>
-      </c>
-      <c r="H21" s="22">
-        <v>23607.600000000006</v>
-      </c>
-      <c r="I21" s="22">
-        <v>732875.58000000007</v>
-      </c>
-      <c r="J21" s="22">
-        <v>-87000</v>
-      </c>
-      <c r="K21" s="22">
-        <v>40837</v>
-      </c>
-      <c r="L21" s="23">
-        <v>299782.6100000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="34">
+      <c r="B19" s="30">
         <v>-0.61000749486272465</v>
       </c>
-      <c r="C22" s="34">
+      <c r="C19" s="30">
         <v>-1.7941700476358673</v>
       </c>
-      <c r="D22" s="34">
+      <c r="D19" s="30">
         <v>0.22769611174560214</v>
       </c>
-      <c r="E22" s="34">
+      <c r="E19" s="30">
         <v>-0.1640673440281494</v>
       </c>
-      <c r="F22" s="34">
+      <c r="F19" s="30">
         <v>0.28555578439541035</v>
       </c>
-      <c r="G22" s="34">
+      <c r="G19" s="30">
         <v>-0.50813781183198103</v>
       </c>
-      <c r="H22" s="34">
+      <c r="H19" s="30">
         <v>0.14080387443860604</v>
       </c>
-      <c r="I22" s="34">
+      <c r="I19" s="30">
         <v>0.35283579373367019</v>
       </c>
-      <c r="J22" s="34">
+      <c r="J19" s="30">
         <v>-0.88775510204081631</v>
       </c>
-      <c r="K22" s="34">
+      <c r="K19" s="30">
         <v>0.28989756294944879</v>
       </c>
-      <c r="L22" s="35">
+      <c r="L19" s="31">
         <v>6.1382762769501956E-2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="2">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/P&L_Rent_Projects_F.xlsx
+++ b/P&L_Rent_Projects_F.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\سدرة الخير\Hub Project Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D5FAA1D-0545-4F0D-8583-E36D1717CA9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10929D9F-1A2D-4A79-9ECB-0F225F779C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{D8720DA4-03DD-471F-8DC0-E7471CF99247}"/>
   </bookViews>
@@ -69,9 +69,6 @@
     <t>Occupancy Rate</t>
   </si>
   <si>
-    <t>Improvements (Assets)</t>
-  </si>
-  <si>
     <t>Net Revenue</t>
   </si>
   <si>
@@ -84,9 +81,6 @@
     <t>Maintenance &amp; Repairs</t>
   </si>
   <si>
-    <t>Utilities (Electricity &amp; Water)</t>
-  </si>
-  <si>
     <t>Marketing</t>
   </si>
   <si>
@@ -96,19 +90,25 @@
     <t>Operating Income</t>
   </si>
   <si>
-    <t>Operating Income Margin (%)</t>
-  </si>
-  <si>
     <t>Net Profit</t>
   </si>
   <si>
-    <t>Net Profit Margin (%)</t>
-  </si>
-  <si>
     <t>2. OPERATING EXPENSES</t>
   </si>
   <si>
-    <t>Leasehold Improvements Amortization</t>
+    <t>Improvements Assets</t>
+  </si>
+  <si>
+    <t>Utilities</t>
+  </si>
+  <si>
+    <t>Amortization</t>
+  </si>
+  <si>
+    <t>Operating Income Margin</t>
+  </si>
+  <si>
+    <t>Net Profit Margin</t>
   </si>
 </sst>
 </file>
@@ -121,7 +121,7 @@
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* \-??_);_(@_)"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -159,13 +159,6 @@
       <family val="2"/>
       <charset val="178"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
@@ -244,6 +237,20 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -515,19 +522,7 @@
   </cellStyleXfs>
   <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -536,32 +531,32 @@
     <xf numFmtId="164" fontId="2" fillId="3" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="3" fillId="4" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="3" fillId="4" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="6" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="6" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="3" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -572,14 +567,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -588,8 +595,21 @@
     <cellStyle name="Normal 3" xfId="3" xr:uid="{BCDE9B6F-D371-4E11-8F30-4B0D6DE6CDCA}"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDF5D29"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFDF5D29"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -907,788 +927,787 @@
     <col min="14" max="14" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="2" t="s">
+    <row r="3" spans="1:12" s="35" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="38" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="27"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
-      <c r="L4" s="29"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+      <c r="B4" s="23"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="25"/>
+    </row>
+    <row r="5" spans="1:12" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="2">
         <v>13</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="3">
         <v>28</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="3">
         <v>41</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="3">
         <v>18</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="3">
         <v>31</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="3">
         <v>48</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="3">
         <v>9</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="3">
         <v>51</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="3">
         <v>10</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5" s="3">
         <v>14</v>
       </c>
-      <c r="L5" s="26">
+      <c r="L5" s="22">
         <f>SUM(B5:K5)</f>
         <v>263</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+    <row r="6" spans="1:12" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="4">
         <v>8</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="5">
         <v>22</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="5">
         <v>34</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="5">
         <v>18</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="5">
         <v>30</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="5">
         <v>48</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="5">
         <v>7</v>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="5">
         <v>51</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="5">
         <v>9</v>
       </c>
-      <c r="K6" s="9">
+      <c r="K6" s="5">
         <v>14</v>
       </c>
-      <c r="L6" s="26">
+      <c r="L6" s="22">
         <f>SUM(B6:K6)</f>
         <v>241</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+    <row r="7" spans="1:12" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="6">
         <f>B6/B5</f>
         <v>0.61538461538461542</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="6">
         <f t="shared" ref="C7:K7" si="0">C6/C5</f>
         <v>0.7857142857142857</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="6">
         <f t="shared" si="0"/>
         <v>0.82926829268292679</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="6">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="6">
         <f t="shared" si="0"/>
         <v>0.967741935483871</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="6">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="6">
         <f t="shared" si="0"/>
         <v>0.77777777777777779</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="6">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J7" s="10">
+      <c r="J7" s="6">
         <f t="shared" si="0"/>
         <v>0.9</v>
       </c>
-      <c r="K7" s="10">
+      <c r="K7" s="6">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L7" s="11">
+      <c r="L7" s="7">
         <f>L6/L5</f>
         <v>0.91634980988593151</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+    <row r="8" spans="1:12" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="8">
+        <v>263984.25</v>
+      </c>
+      <c r="C8" s="9">
+        <v>1053228.27</v>
+      </c>
+      <c r="D8" s="9">
+        <v>563328.69999999995</v>
+      </c>
+      <c r="E8" s="9">
+        <v>876392.56</v>
+      </c>
+      <c r="F8" s="9">
+        <v>300146.36</v>
+      </c>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9">
+        <v>220379.96</v>
+      </c>
+      <c r="I8" s="9">
+        <v>716213.33000000007</v>
+      </c>
+      <c r="J8" s="9">
+        <v>335924.65</v>
+      </c>
+      <c r="K8" s="9">
+        <v>654450.31999999995</v>
+      </c>
+      <c r="L8" s="26">
+        <f>SUM(B8:K8)</f>
+        <v>4984048.4000000004</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="12">
-        <v>263984.25</v>
-      </c>
-      <c r="C8" s="13">
-        <v>1053228.27</v>
-      </c>
-      <c r="D8" s="13">
-        <v>563328.69999999995</v>
-      </c>
-      <c r="E8" s="13">
-        <v>876392.56</v>
-      </c>
-      <c r="F8" s="13">
-        <v>300146.36</v>
-      </c>
-      <c r="G8" s="13">
-        <v>250000</v>
-      </c>
-      <c r="H8" s="13">
-        <v>220379.96</v>
-      </c>
-      <c r="I8" s="13">
-        <v>716213.33000000007</v>
-      </c>
-      <c r="J8" s="13">
-        <v>335924.65</v>
-      </c>
-      <c r="K8" s="13">
-        <v>654450.31999999995</v>
-      </c>
-      <c r="L8" s="30">
-        <f>SUM(B8:K8)</f>
-        <v>5234048.4000000004</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="14" t="s">
+      <c r="B10" s="11">
+        <v>219918</v>
+      </c>
+      <c r="C10" s="11">
+        <v>316336</v>
+      </c>
+      <c r="D10" s="11">
+        <v>682419</v>
+      </c>
+      <c r="E10" s="11">
+        <v>268317</v>
+      </c>
+      <c r="F10" s="11">
+        <v>652420</v>
+      </c>
+      <c r="G10" s="11">
+        <v>809020</v>
+      </c>
+      <c r="H10" s="11">
+        <v>220924</v>
+      </c>
+      <c r="I10" s="11">
+        <v>1374819</v>
+      </c>
+      <c r="J10" s="11">
+        <v>155000</v>
+      </c>
+      <c r="K10" s="11">
+        <v>124000</v>
+      </c>
+      <c r="L10" s="12">
+        <f>SUM(B10:K10)</f>
+        <v>4823173</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="27"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
+      <c r="K11" s="28"/>
+      <c r="L11" s="29"/>
+    </row>
+    <row r="12" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="31"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="32"/>
+    </row>
+    <row r="13" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="15">
-        <v>219918</v>
-      </c>
-      <c r="C10" s="15">
-        <v>316336</v>
-      </c>
-      <c r="D10" s="15">
-        <v>682419</v>
-      </c>
-      <c r="E10" s="15">
-        <v>268317</v>
-      </c>
-      <c r="F10" s="15">
-        <v>652420</v>
-      </c>
-      <c r="G10" s="15">
-        <v>809020</v>
-      </c>
-      <c r="H10" s="15">
-        <v>220924</v>
-      </c>
-      <c r="I10" s="15">
-        <v>1374819</v>
-      </c>
-      <c r="J10" s="15">
-        <v>180317</v>
-      </c>
-      <c r="K10" s="15">
-        <v>124334</v>
-      </c>
-      <c r="L10" s="16">
-        <f>SUM(B10:K10)</f>
-        <v>4848824</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="31"/>
-      <c r="B11" s="32"/>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
-      <c r="K11" s="32"/>
-      <c r="L11" s="33"/>
-    </row>
-    <row r="12" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="34" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="35"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="35"/>
-      <c r="J12" s="35"/>
-      <c r="K12" s="35"/>
-      <c r="L12" s="36"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="18">
+      <c r="B13" s="14">
         <f>SUM(B14:B18)</f>
         <v>290941.11999999994</v>
       </c>
-      <c r="C13" s="18">
+      <c r="C13" s="14">
         <f t="shared" ref="C13:K13" si="1">SUM(C14:C18)</f>
-        <v>451587.02</v>
-      </c>
-      <c r="D13" s="18">
+        <v>459887.02</v>
+      </c>
+      <c r="D13" s="14">
         <f t="shared" si="1"/>
-        <v>693665.86</v>
-      </c>
-      <c r="E13" s="18">
+        <v>692165.86</v>
+      </c>
+      <c r="E13" s="14">
         <f t="shared" si="1"/>
         <v>230778.64</v>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="14">
         <f t="shared" si="1"/>
-        <v>237423.13</v>
-      </c>
-      <c r="G13" s="18">
+        <v>247323.13</v>
+      </c>
+      <c r="G13" s="14">
         <f t="shared" si="1"/>
-        <v>568242.03</v>
-      </c>
-      <c r="H13" s="18">
+        <v>565242.03</v>
+      </c>
+      <c r="H13" s="14">
         <f t="shared" si="1"/>
         <v>128822.27</v>
       </c>
-      <c r="I13" s="18">
+      <c r="I13" s="14">
         <f t="shared" si="1"/>
         <v>752242.98</v>
       </c>
-      <c r="J13" s="18">
+      <c r="J13" s="14">
         <f t="shared" si="1"/>
         <v>24756.3</v>
       </c>
-      <c r="K13" s="18">
+      <c r="K13" s="14">
         <f t="shared" si="1"/>
-        <v>41477.61</v>
-      </c>
-      <c r="L13" s="19">
+        <v>45058.61</v>
+      </c>
+      <c r="L13" s="15">
         <f>SUM(B13:K13)</f>
-        <v>3419936.9599999995</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="21">
+        <v>3437217.9599999995</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="17">
         <v>231087.71</v>
       </c>
-      <c r="C14" s="21">
+      <c r="C14" s="17">
         <v>411748.63</v>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="17">
         <v>561834.06000000006</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="17">
         <v>200000</v>
       </c>
-      <c r="F14" s="21">
+      <c r="F14" s="17">
         <v>198907.1</v>
       </c>
-      <c r="G14" s="21">
+      <c r="G14" s="17">
         <v>466032.61</v>
       </c>
-      <c r="H14" s="21">
+      <c r="H14" s="17">
         <v>79347.83</v>
       </c>
-      <c r="I14" s="21">
+      <c r="I14" s="17">
         <v>631267.80000000005</v>
       </c>
-      <c r="J14" s="21">
+      <c r="J14" s="17">
         <v>24262.3</v>
       </c>
-      <c r="K14" s="21">
+      <c r="K14" s="17">
         <v>40983.61</v>
       </c>
-      <c r="L14" s="22">
+      <c r="L14" s="18">
         <f>SUM(B14:K14)</f>
         <v>2845471.65</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="21">
+    <row r="15" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="17">
         <v>31965</v>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="17">
         <v>4684</v>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="17">
         <v>65975.83</v>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="17">
         <v>10924.509999999998</v>
       </c>
-      <c r="F15" s="21">
+      <c r="F15" s="17">
         <v>8876.27</v>
       </c>
-      <c r="G15" s="21">
+      <c r="G15" s="17">
         <v>15161.13</v>
       </c>
-      <c r="H15" s="21">
+      <c r="H15" s="17">
         <v>5943</v>
       </c>
-      <c r="I15" s="21">
+      <c r="I15" s="17">
         <v>25568.35</v>
       </c>
-      <c r="J15" s="21">
+      <c r="J15" s="17">
         <v>0</v>
       </c>
-      <c r="K15" s="21">
+      <c r="K15" s="17">
         <v>0</v>
       </c>
-      <c r="L15" s="22">
+      <c r="L15" s="18">
         <f t="shared" ref="L15:L18" si="2">SUM(B15:K15)</f>
         <v>169098.09</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="21">
+    <row r="16" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="17">
         <v>11226.41</v>
       </c>
-      <c r="C16" s="21">
+      <c r="C16" s="17">
         <v>22528.39</v>
       </c>
-      <c r="D16" s="21">
+      <c r="D16" s="17">
         <v>44012.97</v>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="17">
         <v>6154.22</v>
       </c>
-      <c r="F16" s="21">
+      <c r="F16" s="17">
         <v>20102.759999999998</v>
       </c>
-      <c r="G16" s="21">
+      <c r="G16" s="17">
         <v>65241.29</v>
       </c>
-      <c r="H16" s="21">
+      <c r="H16" s="17">
         <v>26900.44</v>
       </c>
-      <c r="I16" s="21">
+      <c r="I16" s="17">
         <v>75576.83</v>
       </c>
-      <c r="J16" s="21">
+      <c r="J16" s="17">
         <v>0</v>
       </c>
-      <c r="K16" s="21">
-        <v>0</v>
-      </c>
-      <c r="L16" s="22">
+      <c r="K16" s="17">
+        <v>3581</v>
+      </c>
+      <c r="L16" s="18">
         <f t="shared" si="2"/>
-        <v>271743.31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="21">
+        <v>275324.31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="17">
         <v>2462</v>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="17">
         <v>2926</v>
       </c>
-      <c r="D17" s="21">
+      <c r="D17" s="17">
         <v>2343</v>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="17">
         <v>2699.91</v>
       </c>
-      <c r="F17" s="21">
+      <c r="F17" s="17">
         <v>1437</v>
       </c>
-      <c r="G17" s="21">
+      <c r="G17" s="17">
         <v>807</v>
       </c>
-      <c r="H17" s="21">
+      <c r="H17" s="17">
         <v>1231</v>
       </c>
-      <c r="I17" s="21">
+      <c r="I17" s="17">
         <v>1830</v>
       </c>
-      <c r="J17" s="21">
+      <c r="J17" s="17">
         <v>494</v>
       </c>
-      <c r="K17" s="21">
+      <c r="K17" s="17">
         <v>494</v>
       </c>
-      <c r="L17" s="22">
+      <c r="L17" s="18">
         <f t="shared" si="2"/>
         <v>16723.91</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" s="21">
+    <row r="18" spans="1:14" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="17">
         <v>14200</v>
       </c>
-      <c r="C18" s="21">
-        <v>9700</v>
-      </c>
-      <c r="D18" s="21">
-        <v>19500</v>
-      </c>
-      <c r="E18" s="21">
+      <c r="C18" s="17">
+        <v>18000</v>
+      </c>
+      <c r="D18" s="17">
+        <v>18000</v>
+      </c>
+      <c r="E18" s="17">
         <v>11000</v>
       </c>
-      <c r="F18" s="21">
-        <v>8100</v>
-      </c>
-      <c r="G18" s="21">
-        <v>21000</v>
-      </c>
-      <c r="H18" s="21">
+      <c r="F18" s="17">
+        <v>18000</v>
+      </c>
+      <c r="G18" s="17">
+        <v>18000</v>
+      </c>
+      <c r="H18" s="17">
         <v>15400</v>
       </c>
-      <c r="I18" s="21">
+      <c r="I18" s="17">
         <v>18000</v>
       </c>
-      <c r="J18" s="21">
+      <c r="J18" s="17">
         <v>0</v>
       </c>
-      <c r="K18" s="21">
+      <c r="K18" s="17">
         <v>0</v>
       </c>
-      <c r="L18" s="22">
+      <c r="L18" s="18">
         <f t="shared" si="2"/>
-        <v>116900</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="15">
+        <v>130600</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="11">
         <f>B10-B13</f>
         <v>-71023.119999999937</v>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="11">
         <f t="shared" ref="C19:K19" si="3">C10-C13</f>
-        <v>-135251.02000000002</v>
-      </c>
-      <c r="D19" s="15">
+        <v>-143551.02000000002</v>
+      </c>
+      <c r="D19" s="11">
         <f t="shared" si="3"/>
-        <v>-11246.859999999986</v>
-      </c>
-      <c r="E19" s="15">
+        <v>-9746.859999999986</v>
+      </c>
+      <c r="E19" s="11">
         <f t="shared" si="3"/>
         <v>37538.359999999986</v>
       </c>
-      <c r="F19" s="15">
+      <c r="F19" s="11">
         <f>F10-F13</f>
-        <v>414996.87</v>
-      </c>
-      <c r="G19" s="15">
+        <v>405096.87</v>
+      </c>
+      <c r="G19" s="11">
         <f t="shared" si="3"/>
-        <v>240777.96999999997</v>
-      </c>
-      <c r="H19" s="15">
+        <v>243777.96999999997</v>
+      </c>
+      <c r="H19" s="11">
         <f t="shared" si="3"/>
         <v>92101.73</v>
       </c>
-      <c r="I19" s="15">
+      <c r="I19" s="11">
         <f t="shared" si="3"/>
         <v>622576.02</v>
       </c>
-      <c r="J19" s="15">
+      <c r="J19" s="11">
         <f t="shared" si="3"/>
-        <v>155560.70000000001</v>
-      </c>
-      <c r="K19" s="15">
+        <v>130243.7</v>
+      </c>
+      <c r="K19" s="11">
         <f t="shared" si="3"/>
-        <v>82856.39</v>
-      </c>
-      <c r="L19" s="16">
+        <v>78941.39</v>
+      </c>
+      <c r="L19" s="12">
         <f>SUM(B19:K19)</f>
-        <v>1428887.04</v>
-      </c>
-      <c r="N19" s="37"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" s="24">
+        <v>1385955.04</v>
+      </c>
+      <c r="N19" s="33"/>
+    </row>
+    <row r="20" spans="1:14" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="20">
         <f>B19/B10</f>
         <v>-0.32295273692921878</v>
       </c>
-      <c r="C20" s="24">
+      <c r="C20" s="20">
         <f t="shared" ref="C20:K20" si="4">C19/C10</f>
-        <v>-0.42755494158110369</v>
-      </c>
-      <c r="D20" s="24">
+        <v>-0.45379286581356537</v>
+      </c>
+      <c r="D20" s="20">
         <f t="shared" si="4"/>
-        <v>-1.6480871722504776E-2</v>
-      </c>
-      <c r="E20" s="24">
+        <v>-1.4282808655679262E-2</v>
+      </c>
+      <c r="E20" s="20">
         <f t="shared" si="4"/>
         <v>0.13990302515308381</v>
       </c>
-      <c r="F20" s="24">
+      <c r="F20" s="20">
         <f t="shared" si="4"/>
-        <v>0.63608851659973631</v>
-      </c>
-      <c r="G20" s="24">
+        <v>0.62091424235921644</v>
+      </c>
+      <c r="G20" s="20">
         <f t="shared" si="4"/>
-        <v>0.29761683271118139</v>
-      </c>
-      <c r="H20" s="24">
+        <v>0.30132502286717261</v>
+      </c>
+      <c r="H20" s="20">
         <f t="shared" si="4"/>
         <v>0.41689327551556188</v>
       </c>
-      <c r="I20" s="24">
+      <c r="I20" s="20">
         <f t="shared" si="4"/>
         <v>0.4528421704966254</v>
       </c>
-      <c r="J20" s="24">
+      <c r="J20" s="20">
         <f t="shared" si="4"/>
-        <v>0.86270678860007655</v>
-      </c>
-      <c r="K20" s="24">
+        <v>0.84028193548387098</v>
+      </c>
+      <c r="K20" s="20">
         <f t="shared" si="4"/>
-        <v>0.66640170830183221</v>
-      </c>
-      <c r="L20" s="25">
+        <v>0.63662411290322585</v>
+      </c>
+      <c r="L20" s="21">
         <f>L19/L10</f>
-        <v>0.29468733862066349</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="31"/>
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
-      <c r="L21" s="33"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="21">
+        <v>0.28735337504999303</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="27"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
+      <c r="I21" s="28"/>
+      <c r="J21" s="28"/>
+      <c r="K21" s="28"/>
+      <c r="L21" s="29"/>
+    </row>
+    <row r="22" spans="1:14" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="17">
         <v>24451.599999999999</v>
       </c>
-      <c r="C22" s="21">
+      <c r="C22" s="17">
         <v>58496.13</v>
       </c>
-      <c r="D22" s="21">
+      <c r="D22" s="17">
         <v>116635.05</v>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="17">
         <v>50922.77</v>
       </c>
-      <c r="F22" s="21">
+      <c r="F22" s="17">
         <v>23405.02</v>
       </c>
-      <c r="G22" s="21">
+      <c r="G22" s="17">
         <v>0</v>
       </c>
-      <c r="H22" s="21">
+      <c r="H22" s="17">
         <v>14530.55</v>
       </c>
-      <c r="I22" s="21">
+      <c r="I22" s="17">
         <v>86194.86</v>
       </c>
-      <c r="J22" s="21">
+      <c r="J22" s="17">
         <v>0</v>
       </c>
-      <c r="K22" s="21">
+      <c r="K22" s="17">
         <v>0</v>
       </c>
-      <c r="L22" s="19">
+      <c r="L22" s="15">
         <f>SUM(B22:K22)</f>
         <v>374635.98</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="15">
+    <row r="23" spans="1:14" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="11">
         <f>B19-B22</f>
         <v>-95474.719999999943</v>
       </c>
-      <c r="C23" s="15">
+      <c r="C23" s="11">
         <f t="shared" ref="C23:K23" si="5">C19-C22</f>
-        <v>-193747.15000000002</v>
-      </c>
-      <c r="D23" s="15">
+        <v>-202047.15000000002</v>
+      </c>
+      <c r="D23" s="11">
         <f t="shared" si="5"/>
-        <v>-127881.90999999999</v>
-      </c>
-      <c r="E23" s="15">
+        <v>-126381.90999999999</v>
+      </c>
+      <c r="E23" s="11">
         <f t="shared" si="5"/>
         <v>-13384.410000000011</v>
       </c>
-      <c r="F23" s="15">
+      <c r="F23" s="11">
         <f t="shared" si="5"/>
-        <v>391591.85</v>
-      </c>
-      <c r="G23" s="15">
+        <v>381691.85</v>
+      </c>
+      <c r="G23" s="11">
         <f t="shared" si="5"/>
-        <v>240777.96999999997</v>
-      </c>
-      <c r="H23" s="15">
+        <v>243777.96999999997</v>
+      </c>
+      <c r="H23" s="11">
         <f t="shared" si="5"/>
         <v>77571.179999999993</v>
       </c>
-      <c r="I23" s="15">
+      <c r="I23" s="11">
         <f t="shared" si="5"/>
         <v>536381.16</v>
       </c>
-      <c r="J23" s="15">
+      <c r="J23" s="11">
         <f t="shared" si="5"/>
-        <v>155560.70000000001</v>
-      </c>
-      <c r="K23" s="15">
+        <v>130243.7</v>
+      </c>
+      <c r="K23" s="11">
         <f t="shared" si="5"/>
-        <v>82856.39</v>
-      </c>
-      <c r="L23" s="16">
+        <v>78941.39</v>
+      </c>
+      <c r="L23" s="12">
         <f>L19-L22</f>
-        <v>1054251.06</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="24">
+        <v>1011319.06</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" s="20">
         <f>B23/B10</f>
         <v>-0.43413781500377385</v>
       </c>
-      <c r="C24" s="24">
+      <c r="C24" s="20">
         <f t="shared" ref="C24:K24" si="6">C23/C10</f>
-        <v>-0.61247265565727593</v>
-      </c>
-      <c r="D24" s="24">
+        <v>-0.63871057988973756</v>
+      </c>
+      <c r="D24" s="20">
         <f t="shared" si="6"/>
-        <v>-0.18739500219073618</v>
-      </c>
-      <c r="E24" s="24">
+        <v>-0.18519693912391066</v>
+      </c>
+      <c r="E24" s="20">
         <f t="shared" si="6"/>
         <v>-4.9882825165755471E-2</v>
       </c>
-      <c r="F24" s="24">
+      <c r="F24" s="20">
         <f t="shared" si="6"/>
-        <v>0.60021435578308446</v>
-      </c>
-      <c r="G24" s="24">
+        <v>0.58504008154256459</v>
+      </c>
+      <c r="G24" s="20">
         <f t="shared" si="6"/>
-        <v>0.29761683271118139</v>
-      </c>
-      <c r="H24" s="24">
+        <v>0.30132502286717261</v>
+      </c>
+      <c r="H24" s="20">
         <f t="shared" si="6"/>
         <v>0.35112156216617474</v>
       </c>
-      <c r="I24" s="24">
+      <c r="I24" s="20">
         <f t="shared" si="6"/>
         <v>0.39014674658991477</v>
       </c>
-      <c r="J24" s="24">
+      <c r="J24" s="20">
         <f t="shared" si="6"/>
-        <v>0.86270678860007655</v>
-      </c>
-      <c r="K24" s="24">
+        <v>0.84028193548387098</v>
+      </c>
+      <c r="K24" s="20">
         <f t="shared" si="6"/>
-        <v>0.66640170830183221</v>
-      </c>
-      <c r="L24" s="38">
+        <v>0.63662411290322585</v>
+      </c>
+      <c r="L24" s="34">
         <f>L23/L10</f>
-        <v>0.21742407231114186</v>
-      </c>
-    </row>
+        <v>0.2096792008082646</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="F27" s="37"/>
+      <c r="F27" s="33"/>
     </row>
     <row r="34" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F34" s="37"/>
+      <c r="F34" s="33"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
